--- a/data/trans_orig/IP3111_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP3111_2023-Provincia-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1695</t>
+          <t>1444</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8713</t>
+          <t>8308</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6814</t>
+          <t>6566</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3564</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12420</t>
+          <t>12028</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3083</t>
+          <t>3156</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17032</t>
+          <t>17216</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5535</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18673</t>
+          <t>18601</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10242</t>
+          <t>10005</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28423</t>
+          <t>28913</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,8%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8633</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30912</t>
+          <t>29580</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8390</t>
+          <t>8125</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21143</t>
+          <t>21007</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20155</t>
+          <t>19263</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43509</t>
+          <t>45401</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>31,1%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23944</t>
+          <t>23729</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42023</t>
+          <t>41855</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27278</t>
+          <t>26855</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43007</t>
+          <t>43173</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56456</t>
+          <t>56514</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80816</t>
+          <t>81686</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,95%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5695</t>
+          <t>5405</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17546</t>
+          <t>17892</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6795</t>
+          <t>6883</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18630</t>
+          <t>17705</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14867</t>
+          <t>15106</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31307</t>
+          <t>32115</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4365</t>
+          <t>4117</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5316</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7514</t>
+          <t>6584</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23669</t>
+          <t>23515</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9696</t>
+          <t>9277</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22735</t>
+          <t>21790</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19690</t>
+          <t>19747</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>42087</t>
+          <t>41153</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,33%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>5124</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18945</t>
+          <t>18551</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17033</t>
+          <t>16841</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39371</t>
+          <t>39609</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>23726</t>
+          <t>24009</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>52677</t>
+          <t>52722</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13903</t>
+          <t>14028</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41307</t>
+          <t>41125</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24936</t>
+          <t>25906</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46058</t>
+          <t>46352</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43746</t>
+          <t>45271</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80968</t>
+          <t>80675</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,0%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13856</t>
+          <t>12465</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40682</t>
+          <t>41578</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20860</t>
+          <t>21990</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>41784</t>
+          <t>41132</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>40404</t>
+          <t>41238</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>74902</t>
+          <t>75435</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,93%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t>7901</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>79115</t>
+          <t>87017</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29356</t>
+          <t>29063</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>18750</t>
+          <t>18183</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>116484</t>
+          <t>110365</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>43,78%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2341</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11848</t>
+          <t>11917</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14262</t>
+          <t>14038</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7915</t>
+          <t>7834</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22026</t>
+          <t>21644</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4479</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12696</t>
+          <t>13314</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1807</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8436</t>
+          <t>9080</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8035</t>
+          <t>7986</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>19301</t>
+          <t>19179</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7587</t>
+          <t>7290</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16548</t>
+          <t>16667</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14323</t>
+          <t>14276</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26677</t>
+          <t>27388</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24591</t>
+          <t>24735</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>40035</t>
+          <t>39891</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10913</t>
+          <t>10866</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21525</t>
+          <t>21601</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19135</t>
+          <t>18648</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>32028</t>
+          <t>32256</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>33063</t>
+          <t>33183</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>49770</t>
+          <t>49852</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,48%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3193</t>
+          <t>2923</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9875</t>
+          <t>9692</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10169</t>
+          <t>9779</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6447</t>
+          <t>6718</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>16574</t>
+          <t>16792</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2411</t>
+          <t>2256</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9261</t>
+          <t>8720</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9215</t>
+          <t>9307</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5222</t>
+          <t>5554</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14503</t>
+          <t>14564</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5450</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13993</t>
+          <t>14455</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>1836</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9948</t>
+          <t>10333</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8928</t>
+          <t>8737</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>20948</t>
+          <t>20614</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8399</t>
+          <t>8391</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20197</t>
+          <t>20100</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6116</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20525</t>
+          <t>20558</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16271</t>
+          <t>16906</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>35100</t>
+          <t>35288</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,57%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12018</t>
+          <t>12137</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25121</t>
+          <t>24590</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11758</t>
+          <t>11609</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>30323</t>
+          <t>30973</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>26907</t>
+          <t>26823</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>50942</t>
+          <t>50640</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,69%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8426</t>
+          <t>8095</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>20630</t>
+          <t>19546</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>5921</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>21038</t>
+          <t>20656</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>17740</t>
+          <t>17501</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>36795</t>
+          <t>35525</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>25,74%</t>
         </is>
       </c>
     </row>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1629</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12713</t>
+          <t>12388</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1763</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13876</t>
+          <t>12709</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>1199</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8490</t>
+          <t>7819</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>778</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>8879</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>2778</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>13061</t>
+          <t>12779</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>11636</t>
+          <t>11955</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>24481</t>
+          <t>24809</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>5474</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>38960</t>
+          <t>38406</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>23374</t>
+          <t>22830</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>61514</t>
+          <t>64309</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>46,59%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>547</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>4567</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>168</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4115</t>
+          <t>3765</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6476</t>
+          <t>6604</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>12692</t>
+          <t>12896</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>21044</t>
+          <t>20875</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>16771</t>
+          <t>16160</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>26449</t>
+          <t>26502</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>32096</t>
+          <t>32305</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>45005</t>
+          <t>44927</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>59,97%</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>7189</t>
+          <t>7075</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>15244</t>
+          <t>14671</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>5580</t>
+          <t>5951</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>13845</t>
+          <t>13969</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>14520</t>
+          <t>14665</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>25746</t>
+          <t>26531</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>35,41%</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>7472</t>
+          <t>7534</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>7853</t>
+          <t>7875</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>5082</t>
+          <t>4730</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>13099</t>
+          <t>12785</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -4367,7 +4367,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2789</t>
+          <t>2985</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>617</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5649</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6538</t>
+          <t>6579</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>581</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5174</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>580</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5097</t>
+          <t>5552</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -4705,12 +4705,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>2329</t>
+          <t>2238</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>9115</t>
+          <t>9055</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3994</t>
+          <t>3873</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>12153</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>7232</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>17805</t>
+          <t>17666</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -4818,12 +4818,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>8045</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>17007</t>
+          <t>16733</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4833,12 +4833,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>10747</t>
+          <t>10756</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>21084</t>
+          <t>21296</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>20554</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>35933</t>
+          <t>35060</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>35,75%</t>
         </is>
       </c>
     </row>
@@ -4931,12 +4931,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>11582</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>21510</t>
+          <t>21358</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4966,12 +4966,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>14707</t>
+          <t>14607</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>26399</t>
+          <t>26109</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>28952</t>
+          <t>28942</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>44904</t>
+          <t>44036</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>44,9%</t>
         </is>
       </c>
     </row>
@@ -5044,12 +5044,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3153</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>10312</t>
+          <t>10259</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5059,12 +5059,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5079,12 +5079,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3241</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>14175</t>
+          <t>12495</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>7714</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>19887</t>
+          <t>20091</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,49%</t>
         </is>
       </c>
     </row>
@@ -5157,12 +5157,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>667</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5172,12 +5172,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5227,12 +5227,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>6497</t>
+          <t>6583</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -5270,12 +5270,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>760</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>6281</t>
+          <t>6441</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5285,12 +5285,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5305,12 +5305,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1471</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>7025</t>
+          <t>6777</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>10539</t>
+          <t>10590</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -5500,12 +5500,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>33223</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>52025</t>
+          <t>51518</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5515,12 +5515,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5535,12 +5535,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>32440</t>
+          <t>32245</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>54741</t>
+          <t>53581</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5550,12 +5550,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5570,12 +5570,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>71242</t>
+          <t>69606</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>98374</t>
+          <t>99754</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,79%</t>
         </is>
       </c>
     </row>
@@ -5613,12 +5613,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>12210</t>
+          <t>12175</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>29193</t>
+          <t>29027</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5628,12 +5628,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>19944</t>
+          <t>20566</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>42718</t>
+          <t>41486</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>36861</t>
+          <t>36296</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>62506</t>
+          <t>64693</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5698,12 +5698,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>23,21%</t>
         </is>
       </c>
     </row>
@@ -5726,12 +5726,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>12373</t>
+          <t>11851</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>24874</t>
+          <t>25409</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>17024</t>
+          <t>16962</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>34923</t>
+          <t>34244</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>33806</t>
+          <t>32982</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>54334</t>
+          <t>54840</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,67%</t>
         </is>
       </c>
     </row>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>11621</t>
+          <t>12258</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>24832</t>
+          <t>25916</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>7592</t>
+          <t>7279</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>21424</t>
+          <t>20821</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5889,12 +5889,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>22375</t>
+          <t>22805</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>41938</t>
+          <t>42318</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -5952,12 +5952,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>4586</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>14190</t>
+          <t>14456</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5967,47 +5967,47 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>11,69%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>11447</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>5745</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>21555</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>7,38%</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
           <t>3,71%</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>11,47%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>11447</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>6044</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>20997</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>7,38%</t>
-        </is>
-      </c>
-      <c r="O50" s="2" t="inlineStr">
-        <is>
-          <t>3,9%</t>
-        </is>
-      </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>12964</t>
+          <t>12476</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>30518</t>
+          <t>30204</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>11566</t>
+          <t>11803</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>26943</t>
+          <t>26892</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6080,12 +6080,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>22447</t>
+          <t>22810</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>51628</t>
+          <t>50768</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>38761</t>
+          <t>39367</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>71037</t>
+          <t>71510</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,65%</t>
         </is>
       </c>
     </row>
@@ -6295,12 +6295,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>624</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>6053</t>
+          <t>6231</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>580</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>6662</t>
+          <t>6725</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t>2116</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>9997</t>
+          <t>10602</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -6408,12 +6408,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>8498</t>
+          <t>8748</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>21277</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6423,12 +6423,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>12423</t>
+          <t>12658</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>26694</t>
+          <t>26988</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6458,12 +6458,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>23926</t>
+          <t>24288</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>43504</t>
+          <t>44784</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -6521,12 +6521,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>13908</t>
+          <t>13519</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>28356</t>
+          <t>28459</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6536,12 +6536,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6556,12 +6556,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>18104</t>
+          <t>19152</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>36564</t>
+          <t>35554</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6571,12 +6571,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>37127</t>
+          <t>37209</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>59769</t>
+          <t>59514</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,04%</t>
         </is>
       </c>
     </row>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>17412</t>
+          <t>17403</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>31599</t>
+          <t>32733</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6669,12 +6669,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>17028</t>
+          <t>17787</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>33243</t>
+          <t>33517</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>38084</t>
+          <t>37691</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>59358</t>
+          <t>59066</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,88%</t>
         </is>
       </c>
     </row>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>36680</t>
+          <t>35878</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>54538</t>
+          <t>54516</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>37612</t>
+          <t>39274</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>57231</t>
+          <t>58710</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>78481</t>
+          <t>79208</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>106315</t>
+          <t>107311</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,94%</t>
         </is>
       </c>
     </row>
@@ -6860,12 +6860,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>17083</t>
+          <t>16367</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>31394</t>
+          <t>31018</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6875,12 +6875,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6895,12 +6895,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>25428</t>
+          <t>25450</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>44730</t>
+          <t>44732</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6910,7 +6910,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>47174</t>
+          <t>46416</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>71966</t>
+          <t>71686</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,35%</t>
         </is>
       </c>
     </row>
@@ -7090,12 +7090,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>77515</t>
+          <t>75474</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>110500</t>
+          <t>109000</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7105,12 +7105,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7125,12 +7125,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>72019</t>
+          <t>71916</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>103203</t>
+          <t>105058</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>156436</t>
+          <t>156966</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>202343</t>
+          <t>203756</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,65%</t>
         </is>
       </c>
     </row>
@@ -7203,12 +7203,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>91458</t>
+          <t>90944</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>129554</t>
+          <t>131473</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7218,12 +7218,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7238,12 +7238,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>141526</t>
+          <t>140045</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>186054</t>
+          <t>186041</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7253,7 +7253,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>243091</t>
+          <t>241040</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>305736</t>
+          <t>301823</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,7%</t>
         </is>
       </c>
     </row>
@@ -7316,12 +7316,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>119349</t>
+          <t>117069</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>162772</t>
+          <t>162562</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7331,12 +7331,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>146851</t>
+          <t>146559</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>189445</t>
+          <t>188540</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>277598</t>
+          <t>272879</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>339197</t>
+          <t>336200</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,17%</t>
         </is>
       </c>
     </row>
@@ -7429,12 +7429,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>98230</t>
+          <t>100901</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>139265</t>
+          <t>141985</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>106512</t>
+          <t>107541</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>146789</t>
+          <t>145141</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>213906</t>
+          <t>216611</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>271758</t>
+          <t>271559</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -7542,12 +7542,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>80089</t>
+          <t>79793</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>191499</t>
+          <t>192722</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>77547</t>
+          <t>76601</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>118360</t>
+          <t>116508</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>169208</t>
+          <t>172030</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>286309</t>
+          <t>280696</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -7655,12 +7655,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>64341</t>
+          <t>64296</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>96969</t>
+          <t>96381</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7690,12 +7690,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>82406</t>
+          <t>83954</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>141050</t>
+          <t>144583</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7705,12 +7705,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7725,12 +7725,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>156569</t>
+          <t>154387</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>224265</t>
+          <t>217996</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7740,12 +7740,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,67%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP3111_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP3111_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2269</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>853</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4913</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,15%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3908</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1444</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8308</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,47%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,64%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2836</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1109</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6566</t>
+          <t>6558</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,17 +795,17 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6743</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3291</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12028</t>
+          <t>9397</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6239</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10871</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>10,35%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>5,42%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>18,04%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>6929</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3156</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>17216</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>9,7%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>24,11%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10585</t>
+          <t>4173</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5146</t>
+          <t>1752</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18601</t>
+          <t>7814</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>17514</t>
+          <t>10412</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10005</t>
+          <t>6155</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28913</t>
+          <t>15979</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10386</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6506</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>16737</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>17,23%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>10,8%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>27,77%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15768</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>8733</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>29580</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>22,08%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>12,23%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>41,43%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13154</t>
+          <t>10211</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8125</t>
+          <t>6153</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21007</t>
+          <t>15318</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>28922</t>
+          <t>20597</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>19263</t>
+          <t>14416</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>45401</t>
+          <t>28575</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>24,81%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>31259</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>24917</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>37145</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>51,87%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>41,35%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>61,64%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>33469</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>23729</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>41855</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>46,87%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>33,23%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>58,62%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35669</t>
+          <t>28116</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26855</t>
+          <t>21781</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43173</t>
+          <t>33135</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>69137</t>
+          <t>59376</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56514</t>
+          <t>49471</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81686</t>
+          <t>67459</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>58,56%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9354</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5104</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>14645</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>15,52%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>8,47%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>24,3%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>10281</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5405</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>17892</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>14,4%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,57%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>25,06%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11544</t>
+          <t>8372</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6883</t>
+          <t>4742</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17705</t>
+          <t>12564</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>21825</t>
+          <t>17726</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15106</t>
+          <t>11905</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32115</t>
+          <t>24285</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,08%</t>
         </is>
       </c>
     </row>
@@ -1285,72 +1285,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>3794</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>6,3%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1046</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>3405</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3363</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>4,77%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>820</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>4117</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>415</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>4568</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -1398,57 +1398,57 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>12746</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>7948</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>19282</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>11,09%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>6,91%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>16,77%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>15656</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>6584</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>23515</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>12,46%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>5,24%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>18,72%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15119</t>
+          <t>15745</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9277</t>
+          <t>10225</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21790</t>
+          <t>23676</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>30774</t>
+          <t>28491</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19747</t>
+          <t>21626</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>41153</t>
+          <t>37739</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>22966</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>15130</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35919</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>19,98%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>13,16%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>31,25%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>11414</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5124</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>18551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>9,08%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,08%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>14,76%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>25631</t>
+          <t>10689</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16841</t>
+          <t>6329</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39609</t>
+          <t>16187</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>37044</t>
+          <t>33655</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24009</t>
+          <t>24745</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>52722</t>
+          <t>47962</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29162</t>
+          <t>32000</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14028</t>
+          <t>23237</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41125</t>
+          <t>41961</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34649</t>
+          <t>29097</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25906</t>
+          <t>21500</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46352</t>
+          <t>37867</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>63811</t>
+          <t>61096</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45271</t>
+          <t>50372</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80675</t>
+          <t>74953</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>34,98%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>29200</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>20498</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>39532</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>25,4%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>17,83%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>34,39%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>28280</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>12465</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>41578</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>22,51%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>9,92%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>33,09%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>30976</t>
+          <t>26291</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21990</t>
+          <t>18875</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>41132</t>
+          <t>34977</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>59255</t>
+          <t>55491</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>41238</t>
+          <t>44417</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>75435</t>
+          <t>68072</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>31,77%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>34670</t>
+          <t>10919</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7901</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>87017</t>
+          <t>24949</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12595</t>
+          <t>10952</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4851</t>
+          <t>5319</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29063</t>
+          <t>20468</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>47264</t>
+          <t>21871</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>18183</t>
+          <t>13346</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>110365</t>
+          <t>35928</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -2080,72 +2080,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7120</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2977</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>13658</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,19%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>11,88%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>6468</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2341</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>11917</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5,15%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9,48%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7454</t>
+          <t>6559</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3433</t>
+          <t>3364</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14038</t>
+          <t>12138</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>13922</t>
+          <t>13680</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7834</t>
+          <t>8137</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21644</t>
+          <t>21908</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -2193,57 +2193,57 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3786</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1648</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7162</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>6,61%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>8130</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>4706</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>13314</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>14,64%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>8,47%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>23,97%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4411</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>4578</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9080</t>
+          <t>12806</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,22 +2385,22 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>12542</t>
+          <t>11614</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7986</t>
+          <t>7401</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>19179</t>
+          <t>17429</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>18407</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>13306</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>24285</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>32,13%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>23,22%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>42,38%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>11938</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>7290</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>16667</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>21,49%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>13,12%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>30,0%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>20250</t>
+          <t>12093</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14276</t>
+          <t>7762</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27388</t>
+          <t>16986</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>32188</t>
+          <t>30500</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24735</t>
+          <t>23540</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>39891</t>
+          <t>38033</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>34,14%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>22300</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>16472</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>27878</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>38,92%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>28,75%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>48,65%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>15948</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>10866</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>21601</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>28,71%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>19,56%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>38,88%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>25453</t>
+          <t>15493</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18648</t>
+          <t>10578</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>32256</t>
+          <t>20750</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>41401</t>
+          <t>37793</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>33183</t>
+          <t>30645</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>49852</t>
+          <t>46445</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,69%</t>
         </is>
       </c>
     </row>
@@ -2649,72 +2649,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>4703</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>8731</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>8,21%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>15,24%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>5722</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>2923</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>9692</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>10,3%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>5,26%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>17,45%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5254</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2577</t>
+          <t>2522</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9779</t>
+          <t>9572</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>10975</t>
+          <t>10304</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6718</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>16792</t>
+          <t>15782</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -2762,72 +2762,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>4188</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1738</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>7999</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>7,31%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>13,96%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>4594</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>2256</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>8720</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>8,27%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>15,7%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>4727</t>
+          <t>4499</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9307</t>
+          <t>8332</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>8687</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5554</t>
+          <t>4746</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14564</t>
+          <t>13691</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -2875,72 +2875,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>3914</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1604</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>8705</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>6,83%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>15,19%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>9220</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>5161</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>14455</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>16,6%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>9,29%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>26,02%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>4538</t>
+          <t>8599</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1836</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10333</t>
+          <t>13370</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>13758</t>
+          <t>12513</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8737</t>
+          <t>7910</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>20614</t>
+          <t>18164</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,3%</t>
         </is>
       </c>
     </row>
@@ -2988,57 +2988,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>10194</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>4982</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>17945</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>15,52%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>7,58%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>27,31%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>13498</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>8391</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>20100</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>20,26%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>12,59%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>30,16%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>11649</t>
+          <t>13775</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5710</t>
+          <t>8660</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20558</t>
+          <t>20715</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>25147</t>
+          <t>23969</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16906</t>
+          <t>16162</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>35288</t>
+          <t>34121</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,62%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>21090</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>12751</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>30908</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>32,1%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>19,41%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>47,04%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>18163</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>12137</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>24590</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>27,26%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>18,21%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>36,9%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>20830</t>
+          <t>18528</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11609</t>
+          <t>12492</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>30973</t>
+          <t>25604</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>38993</t>
+          <t>39617</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>26823</t>
+          <t>28349</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>50640</t>
+          <t>50835</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>38,17%</t>
         </is>
       </c>
     </row>
@@ -3331,72 +3331,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>10920</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>5451</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>18679</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>16,62%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>28,43%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>13653</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>8095</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>19546</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>20,49%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>12,15%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>29,33%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>12677</t>
+          <t>14500</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>5921</t>
+          <t>9251</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>20656</t>
+          <t>21769</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>26330</t>
+          <t>25421</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>17501</t>
+          <t>16631</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>35525</t>
+          <t>35518</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>26,67%</t>
         </is>
       </c>
     </row>
@@ -3444,107 +3444,107 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>5080</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1689</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>12417</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>7,73%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>18,9%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>5305</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>1456</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>12388</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>7,43%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>17,35%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>5305</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1646</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>12709</t>
+          <t>12612</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -3557,72 +3557,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>2995</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>7844</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>4,56%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>11,94%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>3581</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>1199</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>7819</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>5,37%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>11,73%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>3643</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8879</t>
+          <t>9177</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6651</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>2894</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>12779</t>
+          <t>12791</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -3670,72 +3670,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>15419</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>5651</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>34688</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>23,47%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>8,6%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>52,8%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>17746</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>11955</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>24809</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>26,63%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>17,94%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>37,23%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>17854</t>
+          <t>17043</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5474</t>
+          <t>11260</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>38406</t>
+          <t>24956</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>35600</t>
+          <t>32462</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>22830</t>
+          <t>21057</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>64309</t>
+          <t>54920</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>41,24%</t>
         </is>
       </c>
     </row>
@@ -3783,57 +3783,57 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>65699</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>65699</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>65699</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>66640</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>66640</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>66640</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>71386</t>
+          <t>67489</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>71386</t>
+          <t>67489</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>71386</t>
+          <t>67489</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>138026</t>
+          <t>133187</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>138026</t>
+          <t>133187</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>138026</t>
+          <t>133187</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3900,72 +3900,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>4383</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>11,08%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>4567</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>5,79%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>13,36%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>2063</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>588</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3765</t>
+          <t>5018</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>3543</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1559</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6604</t>
+          <t>7193</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -4013,72 +4013,72 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>20638</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>16146</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>25690</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>52,14%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>40,79%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>64,91%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>17024</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>12896</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>20875</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>49,78%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>37,71%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>61,04%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>21600</t>
+          <t>17834</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>16160</t>
+          <t>13590</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>26502</t>
+          <t>21984</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>38624</t>
+          <t>38472</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>32305</t>
+          <t>31883</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>44927</t>
+          <t>44907</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>59,92%</t>
         </is>
       </c>
     </row>
@@ -4126,72 +4126,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>9073</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>5525</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>13446</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>22,92%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>13,96%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>33,97%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>10629</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>7075</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>14671</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>31,08%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>20,69%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>42,9%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>9157</t>
+          <t>10793</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>5951</t>
+          <t>7133</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>13969</t>
+          <t>15169</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>19786</t>
+          <t>19865</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>14665</t>
+          <t>14058</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>26531</t>
+          <t>25868</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>34,51%</t>
         </is>
       </c>
     </row>
@@ -4239,72 +4239,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>3900</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>1570</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>7255</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>9,85%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>3,97%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>18,33%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>4018</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>7534</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>11,75%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>22,03%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>4161</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1703</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>7875</t>
+          <t>7343</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>8085</t>
+          <t>8061</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>4730</t>
+          <t>4573</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>12785</t>
+          <t>12617</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,83%</t>
         </is>
       </c>
     </row>
@@ -4352,72 +4352,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>2462</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>5874</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>6,22%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>14,84%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>2985</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>2944</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>8,73%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>2445</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>5293</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>6,0%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>2992</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6579</t>
+          <t>6261</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -4465,97 +4465,97 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>585</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>4983</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>5,12%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>12,59%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="P37" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>2194</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>581</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>5174</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>12,71%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>578</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>4995</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -4578,57 +4578,57 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4695,72 +4695,72 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>5951</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>3135</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>10321</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>12,6%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>6,64%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>21,86%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>4915</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>2238</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>9055</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>11,1%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>5,05%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>20,44%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>7072</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3873</t>
+          <t>2275</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>12153</t>
+          <t>8521</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>11987</t>
+          <t>10495</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>7232</t>
+          <t>6430</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>17666</t>
+          <t>15938</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,42%</t>
         </is>
       </c>
     </row>
@@ -4808,72 +4808,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>13557</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>9050</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>18530</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>28,72%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>19,17%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>39,25%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>12204</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>8045</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>16733</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>27,55%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>18,17%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>37,78%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>15337</t>
+          <t>12264</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>10756</t>
+          <t>7959</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>21296</t>
+          <t>17374</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>27541</t>
+          <t>25821</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>20554</t>
+          <t>19940</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>35060</t>
+          <t>32633</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,67%</t>
         </is>
       </c>
     </row>
@@ -4921,72 +4921,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>18041</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>12883</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>23296</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>38,22%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>27,29%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>49,35%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>16259</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>11733</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>21358</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>36,71%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>26,49%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>48,22%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>20401</t>
+          <t>16633</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>14607</t>
+          <t>11688</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>26109</t>
+          <t>21364</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4996,32 +4996,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>36660</t>
+          <t>34674</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>28942</t>
+          <t>28461</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>44036</t>
+          <t>41994</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>45,9%</t>
         </is>
       </c>
     </row>
@@ -5034,72 +5034,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>5951</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>2502</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>11321</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>12,61%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>23,98%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>6157</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>3153</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>10259</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>13,9%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>7,12%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>23,16%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>6760</t>
+          <t>6222</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>12495</t>
+          <t>10675</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5109,32 +5109,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>12917</t>
+          <t>12173</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>20091</t>
+          <t>19010</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
@@ -5147,72 +5147,72 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>2916</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>6,18%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>2169</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>5048</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>11,4%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>566</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>5461</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5222,32 +5222,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>2789</t>
+          <t>2703</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>900</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>5810</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -5260,72 +5260,72 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>3109</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>1266</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>6167</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>6,59%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>13,06%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>2586</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>760</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>6441</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>14,54%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>2520</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>610</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>6777</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5335,32 +5335,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>5628</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>10590</t>
+          <t>9795</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -5373,57 +5373,57 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5448,17 +5448,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5490,72 +5490,72 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>38613</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>28772</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>48157</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>27,47%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>20,47%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>34,26%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>42226</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>33129</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>51518</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>34,14%</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>26,78%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>41,65%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>42316</t>
+          <t>43141</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>32245</t>
+          <t>34830</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>53581</t>
+          <t>52427</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5565,32 +5565,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>84541</t>
+          <t>81755</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>69606</t>
+          <t>67818</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>99754</t>
+          <t>95641</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>36,45%</t>
         </is>
       </c>
     </row>
@@ -5603,72 +5603,72 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>26342</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>18095</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>35395</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>18,74%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>12,87%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>25,18%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>19046</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>12175</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>29027</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>15,4%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>9,84%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>23,47%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>29211</t>
+          <t>16323</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>20566</t>
+          <t>10129</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>41486</t>
+          <t>23244</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5678,32 +5678,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>48257</t>
+          <t>42665</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>36296</t>
+          <t>32282</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>64693</t>
+          <t>53657</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>20,45%</t>
         </is>
       </c>
     </row>
@@ -5716,72 +5716,72 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>24405</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>17573</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>33593</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>17,36%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>23,9%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>17863</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>11851</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>25409</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>14,44%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>9,58%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>20,54%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>25417</t>
+          <t>18165</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>16962</t>
+          <t>12433</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>34244</t>
+          <t>26718</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5791,32 +5791,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>43280</t>
+          <t>42571</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>32982</t>
+          <t>32761</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>54840</t>
+          <t>53742</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>20,48%</t>
         </is>
       </c>
     </row>
@@ -5829,72 +5829,72 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>13554</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>7539</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>21419</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>9,64%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>5,36%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>15,24%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>17936</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>12258</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>25916</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>14,5%</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>9,91%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>20,95%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>13088</t>
+          <t>18700</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>7279</t>
+          <t>12360</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>20821</t>
+          <t>27080</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5904,32 +5904,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>31024</t>
+          <t>32253</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>22805</t>
+          <t>24049</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>42318</t>
+          <t>43646</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>16,63%</t>
         </is>
       </c>
     </row>
@@ -5942,72 +5942,72 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>9557</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>5364</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>16750</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>6,8%</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>3,82%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>11,92%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>8267</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>4334</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>14456</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>6,68%</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>11,69%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>11447</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>5745</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>21555</t>
+          <t>14533</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6017,32 +6017,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>19715</t>
+          <t>17935</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>12476</t>
+          <t>11911</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>30204</t>
+          <t>25734</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -6055,72 +6055,72 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>28100</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>19767</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>41045</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>19,99%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>14,06%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>29,2%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>18358</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>11803</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>26892</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>14,84%</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>9,54%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>21,74%</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>33565</t>
+          <t>17114</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>22810</t>
+          <t>11631</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>50768</t>
+          <t>25116</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6130,32 +6130,32 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>51923</t>
+          <t>45215</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>39367</t>
+          <t>34251</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>71510</t>
+          <t>59756</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>22,77%</t>
         </is>
       </c>
     </row>
@@ -6168,57 +6168,57 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6243,17 +6243,17 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6285,72 +6285,72 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>2379</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>467</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>6587</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>4,19%</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>2548</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>6231</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>1,98%</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>4,84%</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>2402</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>804</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>6725</t>
+          <t>6987</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6360,32 +6360,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>4950</t>
+          <t>5178</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>10602</t>
+          <t>10246</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -6398,72 +6398,72 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>19041</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>12603</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>27703</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>12,12%</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>8,02%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>17,63%</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>14026</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>8748</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>21277</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>10,9%</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>6,8%</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>16,54%</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>18729</t>
+          <t>15628</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>12658</t>
+          <t>9590</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>26988</t>
+          <t>24116</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6473,32 +6473,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>32755</t>
+          <t>34669</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>24288</t>
+          <t>25073</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>44784</t>
+          <t>46015</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,6%</t>
         </is>
       </c>
     </row>
@@ -6511,72 +6511,72 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>27493</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>19966</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>37246</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>17,5%</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>12,71%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>23,7%</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>20476</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>13519</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>28459</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>15,91%</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>10,51%</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>22,12%</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>26443</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>19152</t>
+          <t>15077</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>35554</t>
+          <t>31941</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6586,32 +6586,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>46919</t>
+          <t>49997</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>37209</t>
+          <t>38355</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>59514</t>
+          <t>62588</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,21%</t>
         </is>
       </c>
     </row>
@@ -6624,72 +6624,72 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>25161</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>17657</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>33948</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>16,01%</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>11,24%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>21,6%</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>23622</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>17403</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>32733</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>18,36%</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>13,53%</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>25,44%</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>24350</t>
+          <t>25201</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>17787</t>
+          <t>17757</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>33517</t>
+          <t>33884</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6699,32 +6699,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>47971</t>
+          <t>50362</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>37691</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>59066</t>
+          <t>61633</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -6742,32 +6742,32 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>44816</t>
+          <t>48513</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>35878</t>
+          <t>38485</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>54516</t>
+          <t>59907</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6777,32 +6777,32 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>47910</t>
+          <t>47211</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>39274</t>
+          <t>37640</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>58710</t>
+          <t>58121</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6812,32 +6812,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>92726</t>
+          <t>95723</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>79208</t>
+          <t>81315</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>107311</t>
+          <t>109602</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,15%</t>
         </is>
       </c>
     </row>
@@ -6850,72 +6850,72 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>34550</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>25299</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>44730</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>21,99%</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>16,1%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>28,47%</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>23177</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>16367</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>31018</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>18,01%</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>12,72%</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>24,11%</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>34326</t>
+          <t>24556</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>25450</t>
+          <t>17713</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>44732</t>
+          <t>33770</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6925,32 +6925,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>57502</t>
+          <t>59106</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>46416</t>
+          <t>47544</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>71686</t>
+          <t>71836</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>24,35%</t>
         </is>
       </c>
     </row>
@@ -6963,57 +6963,57 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7038,17 +7038,17 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7080,72 +7080,72 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>77418</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>64065</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>93351</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>11,34%</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>9,38%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>13,67%</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>92862</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>75474</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>109000</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>14,28%</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>11,61%</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>16,77%</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>87059</t>
+          <t>92948</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>71916</t>
+          <t>79007</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>105058</t>
+          <t>109340</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7155,32 +7155,32 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>179921</t>
+          <t>170365</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>156966</t>
+          <t>151963</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>203756</t>
+          <t>192118</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -7193,72 +7193,72 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>148281</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>128968</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>170691</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>21,72%</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>18,89%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>110744</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>90944</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>131473</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>17,04%</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>13,99%</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>20,22%</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>162173</t>
+          <t>107532</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>140045</t>
+          <t>92789</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>186041</t>
+          <t>124292</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7268,32 +7268,32 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>272917</t>
+          <t>255813</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>241040</t>
+          <t>232392</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>301823</t>
+          <t>281777</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -7306,67 +7306,67 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>154617</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>135943</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>174878</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>22,65%</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>19,91%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>25,62%</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>139758</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>117069</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>162562</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>21,5%</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>18,01%</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>25,01%</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>167350</t>
+          <t>137396</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>146559</t>
+          <t>119573</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>188540</t>
+          <t>156565</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7381,32 +7381,32 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>307108</t>
+          <t>292014</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>272879</t>
+          <t>264564</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>336200</t>
+          <t>317460</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -7419,72 +7419,72 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>118808</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>101422</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>138677</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>17,4%</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>14,86%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>20,31%</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>119203</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>100901</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>141985</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>18,34%</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>15,52%</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>21,84%</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>125468</t>
+          <t>114291</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>107541</t>
+          <t>98119</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>145141</t>
+          <t>130048</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7494,32 +7494,32 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>244671</t>
+          <t>233099</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>216611</t>
+          <t>208855</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>271559</t>
+          <t>260088</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>20,04%</t>
         </is>
       </c>
     </row>
@@ -7532,72 +7532,72 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>88589</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>71123</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>108099</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>12,98%</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>10,42%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>15,83%</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>108924</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>79793</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>192722</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>16,76%</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>12,27%</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>29,65%</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>94359</t>
+          <t>85677</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>76601</t>
+          <t>72650</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>116508</t>
+          <t>102630</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7607,32 +7607,32 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>203283</t>
+          <t>174266</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>172030</t>
+          <t>151396</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>280696</t>
+          <t>196601</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -7645,72 +7645,72 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>94993</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>76356</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>123374</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>13,91%</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>11,18%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>18,07%</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>78600</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>64296</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>96381</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>12,09%</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>9,89%</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>14,83%</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>104343</t>
+          <t>77390</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>83954</t>
+          <t>63483</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>144583</t>
+          <t>93265</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7720,32 +7720,32 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>182943</t>
+          <t>172384</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>154387</t>
+          <t>149731</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>217996</t>
+          <t>203185</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -7758,57 +7758,57 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>682707</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>682707</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>682707</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
           <t>912</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>650092</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>650092</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>650092</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>938</t>
-        </is>
-      </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>740752</t>
+          <t>615235</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>740752</t>
+          <t>615235</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>740752</t>
+          <t>615235</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -7833,17 +7833,17 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>1390844</t>
+          <t>1297941</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>1390844</t>
+          <t>1297941</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>1390844</t>
+          <t>1297941</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
